--- a/FDI_detection_performances.xlsx
+++ b/FDI_detection_performances.xlsx
@@ -942,28 +942,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>216185</v>
+        <v>215787</v>
       </c>
       <c r="D14" t="n">
-        <v>1350</v>
+        <v>1748</v>
       </c>
       <c r="E14" t="n">
-        <v>5620</v>
+        <v>6018</v>
       </c>
       <c r="F14" t="n">
-        <v>15345</v>
+        <v>14947</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.9707756813417191</v>
+        <v>0.9674381551362683</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9191374663072777</v>
+        <v>0.895297993411201</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.7319341760076318</v>
+        <v>0.7129501550202719</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.814922995220393</v>
+        <v>0.7937865108868827</v>
       </c>
     </row>
     <row r="15">
@@ -1014,28 +1014,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>213778</v>
+        <v>213738</v>
       </c>
       <c r="D16" t="n">
-        <v>3757</v>
+        <v>3797</v>
       </c>
       <c r="E16" t="n">
-        <v>5574</v>
+        <v>5630</v>
       </c>
       <c r="F16" t="n">
-        <v>15391</v>
+        <v>15335</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.9608763102725367</v>
+        <v>0.9604737945492663</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.8037915186964696</v>
+        <v>0.8015366924524358</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.7341283090865729</v>
+        <v>0.731457190555688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7673821454391344</v>
+        <v>0.7648951293114198</v>
       </c>
     </row>
     <row r="17">
